--- a/data/area_km2.xlsx
+++ b/data/area_km2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ana Carolina\Desktop\projeto-mapa-maceio\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C77EF32-6563-4F98-8A0A-5E9B27CAAA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1530523-C3D7-40DA-A536-F04A8AC16F83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
